--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135881488</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>135881494</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>135881497</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>135881498</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135881501</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135874946</v>
       </c>
       <c r="B22" t="n">
-        <v>92032</v>
+        <v>92034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>135874952</v>
       </c>
       <c r="B23" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>135874970</v>
       </c>
       <c r="B24" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>135874978</v>
       </c>
       <c r="B25" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>135874924</v>
       </c>
       <c r="B26" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>135874945</v>
       </c>
       <c r="B27" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>135874976</v>
       </c>
       <c r="B28" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>135881489</v>
       </c>
       <c r="B29" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>135881499</v>
       </c>
       <c r="B30" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>135874706</v>
       </c>
       <c r="B147" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>135874973</v>
       </c>
       <c r="B148" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>135874974</v>
       </c>
       <c r="B149" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135859933</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135858947</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135859541</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135859616</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135859685</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135860007</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135860056</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135860113</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135864226</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135864785</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135874927</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135874917</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135881476</v>
       </c>
       <c r="B14" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>135874961</v>
       </c>
       <c r="B30" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92034</v>
+        <v>92048</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135874916</v>
       </c>
       <c r="B47" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135874920</v>
       </c>
       <c r="B48" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135874922</v>
       </c>
       <c r="B49" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135874938</v>
       </c>
       <c r="B50" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135874944</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135874953</v>
       </c>
       <c r="B52" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>135874972</v>
       </c>
       <c r="B53" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135881474</v>
       </c>
       <c r="B54" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>135881483</v>
       </c>
       <c r="B55" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135881485</v>
       </c>
       <c r="B56" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135881493</v>
       </c>
       <c r="B57" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135881500</v>
       </c>
       <c r="B58" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135881505</v>
       </c>
       <c r="B59" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135949167</v>
       </c>
       <c r="B60" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>135949177</v>
       </c>
       <c r="B61" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135949277</v>
       </c>
       <c r="B62" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135949323</v>
       </c>
       <c r="B63" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>135949328</v>
       </c>
       <c r="B64" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>135949364</v>
       </c>
       <c r="B65" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135949390</v>
       </c>
       <c r="B66" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135949442</v>
       </c>
       <c r="B67" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135949469</v>
       </c>
       <c r="B68" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135949550</v>
       </c>
       <c r="B69" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135949654</v>
       </c>
       <c r="B70" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>135949666</v>
       </c>
       <c r="B71" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>135949718</v>
       </c>
       <c r="B72" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>135949724</v>
       </c>
       <c r="B73" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>135949734</v>
       </c>
       <c r="B74" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>135949744</v>
       </c>
       <c r="B75" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>135949840</v>
       </c>
       <c r="B76" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135949862</v>
       </c>
       <c r="B77" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>135949871</v>
       </c>
       <c r="B78" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>135950098</v>
       </c>
       <c r="B79" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135950119</v>
       </c>
       <c r="B80" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>135950143</v>
       </c>
       <c r="B81" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>135950156</v>
       </c>
       <c r="B82" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>135950224</v>
       </c>
       <c r="B83" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>135950300</v>
       </c>
       <c r="B84" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>135950333</v>
       </c>
       <c r="B85" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>135874943</v>
       </c>
       <c r="B86" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>135859078</v>
       </c>
       <c r="B87" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135874930</v>
       </c>
       <c r="B88" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135874934</v>
       </c>
       <c r="B89" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>135874969</v>
       </c>
       <c r="B90" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135881477</v>
       </c>
       <c r="B91" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>135949521</v>
       </c>
       <c r="B92" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135949686</v>
       </c>
       <c r="B93" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>135949696</v>
       </c>
       <c r="B94" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>135950288</v>
       </c>
       <c r="B95" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>135874919</v>
       </c>
       <c r="B96" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135874921</v>
       </c>
       <c r="B97" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>135874923</v>
       </c>
       <c r="B98" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>135874935</v>
       </c>
       <c r="B99" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135874936</v>
       </c>
       <c r="B100" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>135874956</v>
       </c>
       <c r="B101" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135874957</v>
       </c>
       <c r="B102" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>135881508</v>
       </c>
       <c r="B103" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>135949454</v>
       </c>
       <c r="B104" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>135949462</v>
       </c>
       <c r="B105" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135949558</v>
       </c>
       <c r="B106" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>135950115</v>
       </c>
       <c r="B107" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>135862781</v>
       </c>
       <c r="B108" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>135874959</v>
       </c>
       <c r="B109" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>135874960</v>
       </c>
       <c r="B110" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135874963</v>
       </c>
       <c r="B111" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>135874964</v>
       </c>
       <c r="B112" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>135949350</v>
       </c>
       <c r="B113" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>135874965</v>
       </c>
       <c r="B114" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135874977</v>
       </c>
       <c r="B115" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>135874962</v>
       </c>
       <c r="B116" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>135855768</v>
       </c>
       <c r="B117" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>135856140</v>
       </c>
       <c r="B118" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>135856416</v>
       </c>
       <c r="B119" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>135860346</v>
       </c>
       <c r="B120" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>135866514</v>
       </c>
       <c r="B121" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135869093</v>
       </c>
       <c r="B122" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>135874388</v>
       </c>
       <c r="B123" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>135874644</v>
       </c>
       <c r="B124" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>135874687</v>
       </c>
       <c r="B125" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135881482</v>
       </c>
       <c r="B126" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>135881504</v>
       </c>
       <c r="B127" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>135856696</v>
       </c>
       <c r="B128" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>135857596</v>
       </c>
       <c r="B129" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>135863251</v>
       </c>
       <c r="B130" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>135863729</v>
       </c>
       <c r="B131" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>135866611</v>
       </c>
       <c r="B132" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>135866664</v>
       </c>
       <c r="B133" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>135874094</v>
       </c>
       <c r="B134" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>135874206</v>
       </c>
       <c r="B135" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>135874271</v>
       </c>
       <c r="B136" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>135874471</v>
       </c>
       <c r="B137" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135874519</v>
       </c>
       <c r="B138" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135874555</v>
       </c>
       <c r="B139" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>135874571</v>
       </c>
       <c r="B140" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>135874604</v>
       </c>
       <c r="B141" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>135874664</v>
       </c>
       <c r="B142" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>135874939</v>
       </c>
       <c r="B143" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>135874971</v>
       </c>
       <c r="B144" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>135874975</v>
       </c>
       <c r="B145" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135881487</v>
       </c>
       <c r="B146" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>135881506</v>
       </c>
       <c r="B147" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>135855584</v>
       </c>
       <c r="B148" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>135856270</v>
       </c>
       <c r="B149" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>135856477</v>
       </c>
       <c r="B150" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>135856559</v>
       </c>
       <c r="B151" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>135856614</v>
       </c>
       <c r="B152" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135856877</v>
       </c>
       <c r="B153" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>135858582</v>
       </c>
       <c r="B154" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>135858744</v>
       </c>
       <c r="B155" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>135861015</v>
       </c>
       <c r="B156" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135861090</v>
       </c>
       <c r="B157" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>135861887</v>
       </c>
       <c r="B158" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>135862486</v>
       </c>
       <c r="B159" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135862583</v>
       </c>
       <c r="B160" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135862811</v>
       </c>
       <c r="B161" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>135863010</v>
       </c>
       <c r="B162" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>135863047</v>
       </c>
       <c r="B163" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>135863070</v>
       </c>
       <c r="B164" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>135863446</v>
       </c>
       <c r="B165" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>135863630</v>
       </c>
       <c r="B166" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135863743</v>
       </c>
       <c r="B167" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>135863785</v>
       </c>
       <c r="B168" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>135864377</v>
       </c>
       <c r="B169" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>135866322</v>
       </c>
       <c r="B170" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>135867307</v>
       </c>
       <c r="B171" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>135868572</v>
       </c>
       <c r="B172" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>135868617</v>
       </c>
       <c r="B173" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>135868655</v>
       </c>
       <c r="B174" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>135868970</v>
       </c>
       <c r="B175" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>135869055</v>
       </c>
       <c r="B176" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>135869170</v>
       </c>
       <c r="B177" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>135869209</v>
       </c>
       <c r="B178" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>135869293</v>
       </c>
       <c r="B179" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>135869360</v>
       </c>
       <c r="B180" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>135869401</v>
       </c>
       <c r="B181" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>135874124</v>
       </c>
       <c r="B182" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>135874166</v>
       </c>
       <c r="B183" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135874926</v>
       </c>
       <c r="B184" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>135874929</v>
       </c>
       <c r="B185" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>135874941</v>
       </c>
       <c r="B186" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>135874968</v>
       </c>
       <c r="B187" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>135881510</v>
       </c>
       <c r="B188" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>135881492</v>
       </c>
       <c r="B189" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>135881490</v>
       </c>
       <c r="B190" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>135881495</v>
       </c>
       <c r="B191" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135858133</v>
       </c>
       <c r="B192" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>135863529</v>
       </c>
       <c r="B193" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>135874932</v>
       </c>
       <c r="B194" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135874951</v>
       </c>
       <c r="B195" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>135881491</v>
       </c>
       <c r="B196" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>135881496</v>
       </c>
       <c r="B197" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>135874706</v>
       </c>
       <c r="B198" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>135874973</v>
       </c>
       <c r="B199" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>135874974</v>
       </c>
       <c r="B200" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>135949357</v>
       </c>
       <c r="B201" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>135874918</v>
       </c>
       <c r="B202" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135874931</v>
       </c>
       <c r="B203" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135874933</v>
       </c>
       <c r="B204" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>135881507</v>
       </c>
       <c r="B205" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>135949529</v>
       </c>
       <c r="B206" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>135949675</v>
       </c>
       <c r="B207" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>135949755</v>
       </c>
       <c r="B208" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>135950038</v>
       </c>
       <c r="B209" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>135950125</v>
       </c>
       <c r="B210" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>135874947</v>
       </c>
       <c r="B211" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>135874949</v>
       </c>
       <c r="B212" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>135874958</v>
       </c>
       <c r="B213" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>135874966</v>
       </c>
       <c r="B214" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>135874967</v>
       </c>
       <c r="B215" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>135949995</v>
       </c>
       <c r="B216" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ216"/>
+  <dimension ref="A1:AZ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22930,32 +22930,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135881491</v>
+        <v>136156620</v>
       </c>
       <c r="B196" t="n">
-        <v>5202</v>
+        <v>58143</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22965,13 +22965,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470332</v>
+        <v>470531</v>
       </c>
       <c r="R196" t="n">
-        <v>6742319</v>
+        <v>6742232</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22995,27 +22995,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -23030,24 +23025,24 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135881491</t>
+          <t>https://artportalen.se/Sighting/136156620</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135881496</v>
+        <v>135881491</v>
       </c>
       <c r="B197" t="n">
         <v>5202</v>
@@ -23082,10 +23077,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470350</v>
+        <v>470332</v>
       </c>
       <c r="R197" t="n">
-        <v>6742418</v>
+        <v>6742319</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -23117,7 +23112,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -23127,12 +23122,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Torrgran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23158,66 +23153,54 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135881496</t>
+          <t>https://artportalen.se/Sighting/135881491</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135874706</v>
+        <v>135881496</v>
       </c>
       <c r="B198" t="n">
-        <v>99293</v>
+        <v>5202</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Vattudalen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470372</v>
+        <v>470350</v>
       </c>
       <c r="R198" t="n">
-        <v>6742302</v>
+        <v>6742418</v>
       </c>
       <c r="S198" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -23241,12 +23224,27 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23255,31 +23253,30 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874706</t>
+          <t>https://artportalen.se/Sighting/135881496</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135874973</v>
+        <v>135874706</v>
       </c>
       <c r="B199" t="n">
         <v>99293</v>
@@ -23307,25 +23304,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vattudalen N, Dlr</t>
+          <t>Vattudalen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470380</v>
+        <v>470372</v>
       </c>
       <c r="R199" t="n">
-        <v>6742362</v>
+        <v>6742302</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -23352,56 +23356,42 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>30- tal plantor varav 10 blommande.</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874973</t>
+          <t>https://artportalen.se/Sighting/135874706</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135874974</v>
+        <v>135874973</v>
       </c>
       <c r="B200" t="n">
         <v>99293</v>
@@ -23441,10 +23431,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470379</v>
+        <v>470380</v>
       </c>
       <c r="R200" t="n">
-        <v>6742351</v>
+        <v>6742362</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23476,7 +23466,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -23486,12 +23476,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>10-tal, två blommande.</t>
+          <t>30- tal plantor varav 10 blommande.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23517,13 +23507,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874974</t>
+          <t>https://artportalen.se/Sighting/135874973</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135949357</v>
+        <v>135874974</v>
       </c>
       <c r="B201" t="n">
         <v>99293</v>
@@ -23551,32 +23541,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Vattudalen N, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470341</v>
+        <v>470379</v>
       </c>
       <c r="R201" t="n">
-        <v>6742340</v>
+        <v>6742351</v>
       </c>
       <c r="S201" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -23603,83 +23586,109 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>10-tal, två blommande.</t>
+        </is>
+      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135949357</t>
+          <t>https://artportalen.se/Sighting/135874974</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135874918</v>
+        <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>79201</v>
+        <v>99293</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Vattudalen N, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470509</v>
+        <v>470341</v>
       </c>
       <c r="R202" t="n">
-        <v>6742253</v>
+        <v>6742340</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -23706,51 +23715,42 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874918</t>
+          <t>https://artportalen.se/Sighting/135949357</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135874931</v>
+        <v>135874918</v>
       </c>
       <c r="B203" t="n">
         <v>79201</v>
@@ -23785,10 +23785,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470168</v>
+        <v>470509</v>
       </c>
       <c r="R203" t="n">
-        <v>6742266</v>
+        <v>6742253</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23820,7 +23820,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23856,13 +23856,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874931</t>
+          <t>https://artportalen.se/Sighting/135874918</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135874933</v>
+        <v>135874931</v>
       </c>
       <c r="B204" t="n">
         <v>79201</v>
@@ -23897,10 +23897,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470150</v>
+        <v>470168</v>
       </c>
       <c r="R204" t="n">
-        <v>6742287</v>
+        <v>6742266</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23968,13 +23968,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874933</t>
+          <t>https://artportalen.se/Sighting/135874931</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135881507</v>
+        <v>135874933</v>
       </c>
       <c r="B205" t="n">
         <v>79201</v>
@@ -24005,14 +24005,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Vattudalen, Dlr</t>
+          <t>Vattudalen N, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470210</v>
+        <v>470150</v>
       </c>
       <c r="R205" t="n">
-        <v>6742498</v>
+        <v>6742287</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -24039,27 +24039,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24074,24 +24069,24 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135881507</t>
+          <t>https://artportalen.se/Sighting/135874933</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135949529</v>
+        <v>135881507</v>
       </c>
       <c r="B206" t="n">
         <v>79201</v>
@@ -24120,22 +24115,19 @@
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vattudalen N, Dlr</t>
+          <t>Vattudalen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470106</v>
+        <v>470210</v>
       </c>
       <c r="R206" t="n">
-        <v>6742348</v>
+        <v>6742498</v>
       </c>
       <c r="S206" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -24159,12 +24151,27 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24173,31 +24180,30 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135949529</t>
+          <t>https://artportalen.se/Sighting/135881507</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135949675</v>
+        <v>135949529</v>
       </c>
       <c r="B207" t="n">
         <v>79201</v>
@@ -24235,10 +24241,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470070</v>
+        <v>470106</v>
       </c>
       <c r="R207" t="n">
-        <v>6742468</v>
+        <v>6742348</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -24297,13 +24303,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135949675</t>
+          <t>https://artportalen.se/Sighting/135949529</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>135949755</v>
+        <v>135949675</v>
       </c>
       <c r="B208" t="n">
         <v>79201</v>
@@ -24341,10 +24347,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470017</v>
+        <v>470070</v>
       </c>
       <c r="R208" t="n">
-        <v>6742473</v>
+        <v>6742468</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -24403,13 +24409,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135949755</t>
+          <t>https://artportalen.se/Sighting/135949675</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135950038</v>
+        <v>135949755</v>
       </c>
       <c r="B209" t="n">
         <v>79201</v>
@@ -24447,10 +24453,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>469883</v>
+        <v>470017</v>
       </c>
       <c r="R209" t="n">
-        <v>6742741</v>
+        <v>6742473</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -24509,13 +24515,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135950038</t>
+          <t>https://artportalen.se/Sighting/135949755</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135950125</v>
+        <v>135950038</v>
       </c>
       <c r="B210" t="n">
         <v>79201</v>
@@ -24553,13 +24559,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>469852</v>
+        <v>469883</v>
       </c>
       <c r="R210" t="n">
-        <v>6742806</v>
+        <v>6742741</v>
       </c>
       <c r="S210" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24615,54 +24621,57 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135950125</t>
+          <t>https://artportalen.se/Sighting/135950038</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135874947</v>
+        <v>135950125</v>
       </c>
       <c r="B211" t="n">
-        <v>80508</v>
+        <v>79201</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Vattudalen N, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>469897</v>
+        <v>469852</v>
       </c>
       <c r="R211" t="n">
-        <v>6742480</v>
+        <v>6742806</v>
       </c>
       <c r="S211" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24689,56 +24698,42 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874947</t>
+          <t>https://artportalen.se/Sighting/135950125</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135874949</v>
+        <v>135874947</v>
       </c>
       <c r="B212" t="n">
         <v>80508</v>
@@ -24773,13 +24768,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>469871</v>
+        <v>469897</v>
       </c>
       <c r="R212" t="n">
-        <v>6742497</v>
+        <v>6742480</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24808,7 +24803,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24818,12 +24813,12 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Apotecier</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24849,13 +24844,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874949</t>
+          <t>https://artportalen.se/Sighting/135874947</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135874958</v>
+        <v>135874949</v>
       </c>
       <c r="B213" t="n">
         <v>80508</v>
@@ -24890,10 +24885,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>469995</v>
+        <v>469871</v>
       </c>
       <c r="R213" t="n">
-        <v>6742678</v>
+        <v>6742497</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24925,7 +24920,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24935,12 +24930,12 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Apotecier</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24966,13 +24961,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874958</t>
+          <t>https://artportalen.se/Sighting/135874949</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135874966</v>
+        <v>135874958</v>
       </c>
       <c r="B214" t="n">
         <v>80508</v>
@@ -25007,10 +25002,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470073</v>
+        <v>469995</v>
       </c>
       <c r="R214" t="n">
-        <v>6742634</v>
+        <v>6742678</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -25042,7 +25037,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -25052,7 +25047,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25078,13 +25078,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874966</t>
+          <t>https://artportalen.se/Sighting/135874958</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135874967</v>
+        <v>135874966</v>
       </c>
       <c r="B215" t="n">
         <v>80508</v>
@@ -25119,10 +25119,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>470104</v>
+        <v>470073</v>
       </c>
       <c r="R215" t="n">
-        <v>6742562</v>
+        <v>6742634</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -25154,7 +25154,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -25164,12 +25164,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25195,13 +25190,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135874967</t>
+          <t>https://artportalen.se/Sighting/135874966</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135949995</v>
+        <v>135874967</v>
       </c>
       <c r="B216" t="n">
         <v>80508</v>
@@ -25230,22 +25225,19 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Vattudalen N, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>469967</v>
+        <v>470104</v>
       </c>
       <c r="R216" t="n">
-        <v>6742699</v>
+        <v>6742562</v>
       </c>
       <c r="S216" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -25272,14 +25264,24 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25288,23 +25290,133 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135874967</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>135949995</v>
+      </c>
+      <c r="B217" t="n">
+        <v>80508</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Vattudalen N, Dlr</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>469967</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6742699</v>
+      </c>
+      <c r="S217" t="n">
+        <v>50</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Sollerön</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135949995</t>
         </is>
@@ -25527,6 +25639,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>135874927</v>
       </c>
       <c r="B12" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135874917</v>
       </c>
       <c r="B13" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135881476</v>
       </c>
       <c r="B14" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>135874961</v>
       </c>
       <c r="B30" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135874916</v>
       </c>
       <c r="B47" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135874920</v>
       </c>
       <c r="B48" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135874922</v>
       </c>
       <c r="B49" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135874938</v>
       </c>
       <c r="B50" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135874944</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135874953</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>135874972</v>
       </c>
       <c r="B53" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135881474</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>135881483</v>
       </c>
       <c r="B55" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135881485</v>
       </c>
       <c r="B56" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135881493</v>
       </c>
       <c r="B57" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135881500</v>
       </c>
       <c r="B58" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135881505</v>
       </c>
       <c r="B59" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135949167</v>
       </c>
       <c r="B60" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>135949177</v>
       </c>
       <c r="B61" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135949277</v>
       </c>
       <c r="B62" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135949323</v>
       </c>
       <c r="B63" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>135949328</v>
       </c>
       <c r="B64" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>135949364</v>
       </c>
       <c r="B65" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135949390</v>
       </c>
       <c r="B66" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135949442</v>
       </c>
       <c r="B67" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135949469</v>
       </c>
       <c r="B68" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135949550</v>
       </c>
       <c r="B69" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135949654</v>
       </c>
       <c r="B70" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>135949666</v>
       </c>
       <c r="B71" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>135949718</v>
       </c>
       <c r="B72" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>135949724</v>
       </c>
       <c r="B73" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>135949734</v>
       </c>
       <c r="B74" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>135949744</v>
       </c>
       <c r="B75" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>135949840</v>
       </c>
       <c r="B76" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135949862</v>
       </c>
       <c r="B77" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>135949871</v>
       </c>
       <c r="B78" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>135950098</v>
       </c>
       <c r="B79" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135950119</v>
       </c>
       <c r="B80" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>135950143</v>
       </c>
       <c r="B81" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>135950156</v>
       </c>
       <c r="B82" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>135950224</v>
       </c>
       <c r="B83" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>135950300</v>
       </c>
       <c r="B84" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>135950333</v>
       </c>
       <c r="B85" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>135874943</v>
       </c>
       <c r="B86" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>135859078</v>
       </c>
       <c r="B87" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135874930</v>
       </c>
       <c r="B88" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135874934</v>
       </c>
       <c r="B89" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>135874969</v>
       </c>
       <c r="B90" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135881477</v>
       </c>
       <c r="B91" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>135949521</v>
       </c>
       <c r="B92" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135949686</v>
       </c>
       <c r="B93" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>135949696</v>
       </c>
       <c r="B94" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>135950288</v>
       </c>
       <c r="B95" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>135874919</v>
       </c>
       <c r="B96" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135874921</v>
       </c>
       <c r="B97" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>135874923</v>
       </c>
       <c r="B98" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>135874935</v>
       </c>
       <c r="B99" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135874936</v>
       </c>
       <c r="B100" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>135874956</v>
       </c>
       <c r="B101" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135874957</v>
       </c>
       <c r="B102" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>135881508</v>
       </c>
       <c r="B103" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>135949454</v>
       </c>
       <c r="B104" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>135949462</v>
       </c>
       <c r="B105" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135949558</v>
       </c>
       <c r="B106" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>135950115</v>
       </c>
       <c r="B107" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>135862781</v>
       </c>
       <c r="B108" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>135874959</v>
       </c>
       <c r="B109" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>135874960</v>
       </c>
       <c r="B110" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135874963</v>
       </c>
       <c r="B111" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>135874964</v>
       </c>
       <c r="B112" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>135949350</v>
       </c>
       <c r="B113" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>135874965</v>
       </c>
       <c r="B114" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135874977</v>
       </c>
       <c r="B115" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>135874962</v>
       </c>
       <c r="B116" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135874706</v>
       </c>
       <c r="B199" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>135874973</v>
       </c>
       <c r="B200" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>135874974</v>
       </c>
       <c r="B201" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135874918</v>
       </c>
       <c r="B203" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135874931</v>
       </c>
       <c r="B204" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>135874933</v>
       </c>
       <c r="B205" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>135881507</v>
       </c>
       <c r="B206" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>135949529</v>
       </c>
       <c r="B207" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>135949675</v>
       </c>
       <c r="B208" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>135949755</v>
       </c>
       <c r="B209" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135950038</v>
       </c>
       <c r="B210" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>135950125</v>
       </c>
       <c r="B211" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>135874947</v>
       </c>
       <c r="B212" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>135874949</v>
       </c>
       <c r="B213" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>135874958</v>
       </c>
       <c r="B214" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>135874966</v>
       </c>
       <c r="B215" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>135874967</v>
       </c>
       <c r="B216" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>135949995</v>
       </c>
       <c r="B217" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92049</v>
+        <v>92050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135874706</v>
       </c>
       <c r="B199" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>135874973</v>
       </c>
       <c r="B200" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>135874974</v>
       </c>
       <c r="B201" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135859933</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135858947</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135859541</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135859616</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135859685</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135860007</v>
       </c>
       <c r="B7" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135860056</v>
       </c>
       <c r="B8" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135860113</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135864226</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135864785</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135874927</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135874917</v>
       </c>
       <c r="B13" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135881476</v>
       </c>
       <c r="B14" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>135874961</v>
       </c>
       <c r="B30" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135874916</v>
       </c>
       <c r="B47" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135874920</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135874922</v>
       </c>
       <c r="B49" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135874938</v>
       </c>
       <c r="B50" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135874944</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135874953</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>135874972</v>
       </c>
       <c r="B53" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135881474</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>135881483</v>
       </c>
       <c r="B55" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135881485</v>
       </c>
       <c r="B56" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135881493</v>
       </c>
       <c r="B57" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135881500</v>
       </c>
       <c r="B58" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135881505</v>
       </c>
       <c r="B59" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135949167</v>
       </c>
       <c r="B60" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>135949177</v>
       </c>
       <c r="B61" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135949277</v>
       </c>
       <c r="B62" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135949323</v>
       </c>
       <c r="B63" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>135949328</v>
       </c>
       <c r="B64" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>135949364</v>
       </c>
       <c r="B65" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135949390</v>
       </c>
       <c r="B66" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135949442</v>
       </c>
       <c r="B67" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135949469</v>
       </c>
       <c r="B68" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135949550</v>
       </c>
       <c r="B69" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135949654</v>
       </c>
       <c r="B70" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>135949666</v>
       </c>
       <c r="B71" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>135949718</v>
       </c>
       <c r="B72" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>135949724</v>
       </c>
       <c r="B73" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>135949734</v>
       </c>
       <c r="B74" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>135949744</v>
       </c>
       <c r="B75" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>135949840</v>
       </c>
       <c r="B76" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135949862</v>
       </c>
       <c r="B77" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>135949871</v>
       </c>
       <c r="B78" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>135950098</v>
       </c>
       <c r="B79" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135950119</v>
       </c>
       <c r="B80" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>135950143</v>
       </c>
       <c r="B81" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>135950156</v>
       </c>
       <c r="B82" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>135950224</v>
       </c>
       <c r="B83" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>135950300</v>
       </c>
       <c r="B84" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>135950333</v>
       </c>
       <c r="B85" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>135874943</v>
       </c>
       <c r="B86" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>135859078</v>
       </c>
       <c r="B87" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135874930</v>
       </c>
       <c r="B88" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135874934</v>
       </c>
       <c r="B89" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>135874969</v>
       </c>
       <c r="B90" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135881477</v>
       </c>
       <c r="B91" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>135949521</v>
       </c>
       <c r="B92" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135949686</v>
       </c>
       <c r="B93" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>135949696</v>
       </c>
       <c r="B94" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>135950288</v>
       </c>
       <c r="B95" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>135874919</v>
       </c>
       <c r="B96" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135874921</v>
       </c>
       <c r="B97" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>135874923</v>
       </c>
       <c r="B98" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>135874935</v>
       </c>
       <c r="B99" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135874936</v>
       </c>
       <c r="B100" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>135874956</v>
       </c>
       <c r="B101" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135874957</v>
       </c>
       <c r="B102" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>135881508</v>
       </c>
       <c r="B103" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>135949454</v>
       </c>
       <c r="B104" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>135949462</v>
       </c>
       <c r="B105" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135949558</v>
       </c>
       <c r="B106" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>135950115</v>
       </c>
       <c r="B107" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>135862781</v>
       </c>
       <c r="B108" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>135874959</v>
       </c>
       <c r="B109" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>135874960</v>
       </c>
       <c r="B110" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135874963</v>
       </c>
       <c r="B111" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>135874964</v>
       </c>
       <c r="B112" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>135949350</v>
       </c>
       <c r="B113" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>135874965</v>
       </c>
       <c r="B114" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135874977</v>
       </c>
       <c r="B115" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>135874962</v>
       </c>
       <c r="B116" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>135855768</v>
       </c>
       <c r="B117" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>135856140</v>
       </c>
       <c r="B118" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>135856416</v>
       </c>
       <c r="B119" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>135860346</v>
       </c>
       <c r="B120" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>135866514</v>
       </c>
       <c r="B121" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135869093</v>
       </c>
       <c r="B122" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>135874388</v>
       </c>
       <c r="B123" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>135874644</v>
       </c>
       <c r="B124" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>135874687</v>
       </c>
       <c r="B125" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135881482</v>
       </c>
       <c r="B126" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>135881504</v>
       </c>
       <c r="B127" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>135856696</v>
       </c>
       <c r="B128" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>135857596</v>
       </c>
       <c r="B129" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>135863251</v>
       </c>
       <c r="B130" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>135863729</v>
       </c>
       <c r="B131" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>135866611</v>
       </c>
       <c r="B132" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>135866664</v>
       </c>
       <c r="B133" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>135874094</v>
       </c>
       <c r="B134" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>135874206</v>
       </c>
       <c r="B135" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>135874271</v>
       </c>
       <c r="B136" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>135874471</v>
       </c>
       <c r="B137" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135874519</v>
       </c>
       <c r="B138" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135874555</v>
       </c>
       <c r="B139" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>135874571</v>
       </c>
       <c r="B140" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>135874604</v>
       </c>
       <c r="B141" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>135874664</v>
       </c>
       <c r="B142" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>135874939</v>
       </c>
       <c r="B143" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>135874971</v>
       </c>
       <c r="B144" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>135874975</v>
       </c>
       <c r="B145" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135881487</v>
       </c>
       <c r="B146" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>135881506</v>
       </c>
       <c r="B147" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>135855584</v>
       </c>
       <c r="B148" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>135856270</v>
       </c>
       <c r="B149" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>135856477</v>
       </c>
       <c r="B150" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>135856559</v>
       </c>
       <c r="B151" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>135856614</v>
       </c>
       <c r="B152" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135856877</v>
       </c>
       <c r="B153" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>135858582</v>
       </c>
       <c r="B154" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>135858744</v>
       </c>
       <c r="B155" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>135861015</v>
       </c>
       <c r="B156" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135861090</v>
       </c>
       <c r="B157" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>135861887</v>
       </c>
       <c r="B158" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>135862486</v>
       </c>
       <c r="B159" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135862583</v>
       </c>
       <c r="B160" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135862811</v>
       </c>
       <c r="B161" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>135863010</v>
       </c>
       <c r="B162" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>135863047</v>
       </c>
       <c r="B163" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>135863070</v>
       </c>
       <c r="B164" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>135863446</v>
       </c>
       <c r="B165" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>135863630</v>
       </c>
       <c r="B166" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135863743</v>
       </c>
       <c r="B167" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>135863785</v>
       </c>
       <c r="B168" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>135864377</v>
       </c>
       <c r="B169" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>135866322</v>
       </c>
       <c r="B170" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>135867307</v>
       </c>
       <c r="B171" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>135868572</v>
       </c>
       <c r="B172" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>135868617</v>
       </c>
       <c r="B173" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>135868655</v>
       </c>
       <c r="B174" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>135868970</v>
       </c>
       <c r="B175" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>135869055</v>
       </c>
       <c r="B176" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>135869170</v>
       </c>
       <c r="B177" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>135869209</v>
       </c>
       <c r="B178" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>135869293</v>
       </c>
       <c r="B179" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>135869360</v>
       </c>
       <c r="B180" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>135869401</v>
       </c>
       <c r="B181" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>135874124</v>
       </c>
       <c r="B182" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>135874166</v>
       </c>
       <c r="B183" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135874926</v>
       </c>
       <c r="B184" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>135874929</v>
       </c>
       <c r="B185" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>135874941</v>
       </c>
       <c r="B186" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>135874968</v>
       </c>
       <c r="B187" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>135881510</v>
       </c>
       <c r="B188" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135858133</v>
       </c>
       <c r="B192" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>135863529</v>
       </c>
       <c r="B193" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>135874932</v>
       </c>
       <c r="B194" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135874951</v>
       </c>
       <c r="B195" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>136156620</v>
       </c>
       <c r="B196" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135874706</v>
       </c>
       <c r="B199" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>135874973</v>
       </c>
       <c r="B200" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>135874974</v>
       </c>
       <c r="B201" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135874918</v>
       </c>
       <c r="B203" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135874931</v>
       </c>
       <c r="B204" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>135874933</v>
       </c>
       <c r="B205" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>135881507</v>
       </c>
       <c r="B206" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>135949529</v>
       </c>
       <c r="B207" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>135949675</v>
       </c>
       <c r="B208" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>135949755</v>
       </c>
       <c r="B209" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135950038</v>
       </c>
       <c r="B210" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>135950125</v>
       </c>
       <c r="B211" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>135874947</v>
       </c>
       <c r="B212" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>135874949</v>
       </c>
       <c r="B213" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>135874958</v>
       </c>
       <c r="B214" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>135874966</v>
       </c>
       <c r="B215" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>135874967</v>
       </c>
       <c r="B216" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>135949995</v>
       </c>
       <c r="B217" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135859933</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135858947</v>
       </c>
       <c r="B3" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135859541</v>
       </c>
       <c r="B4" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135859616</v>
       </c>
       <c r="B5" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135859685</v>
       </c>
       <c r="B6" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135860007</v>
       </c>
       <c r="B7" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135860056</v>
       </c>
       <c r="B8" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135860113</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135864226</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135864785</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135874927</v>
       </c>
       <c r="B12" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135874917</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135881476</v>
       </c>
       <c r="B14" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>135874961</v>
       </c>
       <c r="B30" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92051</v>
+        <v>92057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135874916</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135874920</v>
       </c>
       <c r="B48" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135874922</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135874938</v>
       </c>
       <c r="B50" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135874944</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135874953</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>135874972</v>
       </c>
       <c r="B53" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135881474</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>135881483</v>
       </c>
       <c r="B55" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135881485</v>
       </c>
       <c r="B56" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135881493</v>
       </c>
       <c r="B57" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135881500</v>
       </c>
       <c r="B58" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135881505</v>
       </c>
       <c r="B59" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135949167</v>
       </c>
       <c r="B60" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>135949177</v>
       </c>
       <c r="B61" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135949277</v>
       </c>
       <c r="B62" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135949323</v>
       </c>
       <c r="B63" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>135949328</v>
       </c>
       <c r="B64" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>135949364</v>
       </c>
       <c r="B65" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135949390</v>
       </c>
       <c r="B66" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135949442</v>
       </c>
       <c r="B67" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135949469</v>
       </c>
       <c r="B68" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135949550</v>
       </c>
       <c r="B69" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135949654</v>
       </c>
       <c r="B70" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>135949666</v>
       </c>
       <c r="B71" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>135949718</v>
       </c>
       <c r="B72" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>135949724</v>
       </c>
       <c r="B73" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>135949734</v>
       </c>
       <c r="B74" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>135949744</v>
       </c>
       <c r="B75" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>135949840</v>
       </c>
       <c r="B76" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135949862</v>
       </c>
       <c r="B77" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>135949871</v>
       </c>
       <c r="B78" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>135950098</v>
       </c>
       <c r="B79" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135950119</v>
       </c>
       <c r="B80" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>135950143</v>
       </c>
       <c r="B81" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>135950156</v>
       </c>
       <c r="B82" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>135950224</v>
       </c>
       <c r="B83" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>135950300</v>
       </c>
       <c r="B84" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>135950333</v>
       </c>
       <c r="B85" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>135874943</v>
       </c>
       <c r="B86" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>135859078</v>
       </c>
       <c r="B87" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135874930</v>
       </c>
       <c r="B88" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135874934</v>
       </c>
       <c r="B89" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>135874969</v>
       </c>
       <c r="B90" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135881477</v>
       </c>
       <c r="B91" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>135949521</v>
       </c>
       <c r="B92" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135949686</v>
       </c>
       <c r="B93" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>135949696</v>
       </c>
       <c r="B94" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>135950288</v>
       </c>
       <c r="B95" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>135874919</v>
       </c>
       <c r="B96" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135874921</v>
       </c>
       <c r="B97" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>135874923</v>
       </c>
       <c r="B98" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>135874935</v>
       </c>
       <c r="B99" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135874936</v>
       </c>
       <c r="B100" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>135874956</v>
       </c>
       <c r="B101" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135874957</v>
       </c>
       <c r="B102" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>135881508</v>
       </c>
       <c r="B103" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>135949454</v>
       </c>
       <c r="B104" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>135949462</v>
       </c>
       <c r="B105" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135949558</v>
       </c>
       <c r="B106" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>135950115</v>
       </c>
       <c r="B107" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>135862781</v>
       </c>
       <c r="B108" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>135874959</v>
       </c>
       <c r="B109" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>135874960</v>
       </c>
       <c r="B110" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135874963</v>
       </c>
       <c r="B111" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>135874964</v>
       </c>
       <c r="B112" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>135949350</v>
       </c>
       <c r="B113" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>135874965</v>
       </c>
       <c r="B114" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135874977</v>
       </c>
       <c r="B115" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>135874962</v>
       </c>
       <c r="B116" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>135855768</v>
       </c>
       <c r="B117" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>135856140</v>
       </c>
       <c r="B118" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>135856416</v>
       </c>
       <c r="B119" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>135860346</v>
       </c>
       <c r="B120" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>135866514</v>
       </c>
       <c r="B121" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135869093</v>
       </c>
       <c r="B122" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>135874388</v>
       </c>
       <c r="B123" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>135874644</v>
       </c>
       <c r="B124" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>135874687</v>
       </c>
       <c r="B125" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135881482</v>
       </c>
       <c r="B126" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>135881504</v>
       </c>
       <c r="B127" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>135856696</v>
       </c>
       <c r="B128" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>135857596</v>
       </c>
       <c r="B129" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>135863251</v>
       </c>
       <c r="B130" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>135863729</v>
       </c>
       <c r="B131" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>135866611</v>
       </c>
       <c r="B132" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>135866664</v>
       </c>
       <c r="B133" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>135874094</v>
       </c>
       <c r="B134" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>135874206</v>
       </c>
       <c r="B135" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>135874271</v>
       </c>
       <c r="B136" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>135874471</v>
       </c>
       <c r="B137" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135874519</v>
       </c>
       <c r="B138" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135874555</v>
       </c>
       <c r="B139" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>135874571</v>
       </c>
       <c r="B140" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>135874604</v>
       </c>
       <c r="B141" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>135874664</v>
       </c>
       <c r="B142" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>135874939</v>
       </c>
       <c r="B143" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>135874971</v>
       </c>
       <c r="B144" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>135874975</v>
       </c>
       <c r="B145" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135881487</v>
       </c>
       <c r="B146" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>135881506</v>
       </c>
       <c r="B147" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>135855584</v>
       </c>
       <c r="B148" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>135856270</v>
       </c>
       <c r="B149" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>135856477</v>
       </c>
       <c r="B150" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>135856559</v>
       </c>
       <c r="B151" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>135856614</v>
       </c>
       <c r="B152" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135856877</v>
       </c>
       <c r="B153" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>135858582</v>
       </c>
       <c r="B154" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>135858744</v>
       </c>
       <c r="B155" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>135861015</v>
       </c>
       <c r="B156" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135861090</v>
       </c>
       <c r="B157" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>135861887</v>
       </c>
       <c r="B158" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>135862486</v>
       </c>
       <c r="B159" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135862583</v>
       </c>
       <c r="B160" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135862811</v>
       </c>
       <c r="B161" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>135863010</v>
       </c>
       <c r="B162" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>135863047</v>
       </c>
       <c r="B163" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>135863070</v>
       </c>
       <c r="B164" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>135863446</v>
       </c>
       <c r="B165" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>135863630</v>
       </c>
       <c r="B166" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135863743</v>
       </c>
       <c r="B167" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>135863785</v>
       </c>
       <c r="B168" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>135864377</v>
       </c>
       <c r="B169" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>135866322</v>
       </c>
       <c r="B170" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>135867307</v>
       </c>
       <c r="B171" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>135868572</v>
       </c>
       <c r="B172" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>135868617</v>
       </c>
       <c r="B173" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>135868655</v>
       </c>
       <c r="B174" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>135868970</v>
       </c>
       <c r="B175" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>135869055</v>
       </c>
       <c r="B176" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>135869170</v>
       </c>
       <c r="B177" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>135869209</v>
       </c>
       <c r="B178" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>135869293</v>
       </c>
       <c r="B179" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>135869360</v>
       </c>
       <c r="B180" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>135869401</v>
       </c>
       <c r="B181" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>135874124</v>
       </c>
       <c r="B182" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>135874166</v>
       </c>
       <c r="B183" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135874926</v>
       </c>
       <c r="B184" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>135874929</v>
       </c>
       <c r="B185" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>135874941</v>
       </c>
       <c r="B186" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>135874968</v>
       </c>
       <c r="B187" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>135881510</v>
       </c>
       <c r="B188" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135858133</v>
       </c>
       <c r="B192" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>135863529</v>
       </c>
       <c r="B193" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>135874932</v>
       </c>
       <c r="B194" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135874951</v>
       </c>
       <c r="B195" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>136156620</v>
       </c>
       <c r="B196" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135874706</v>
       </c>
       <c r="B199" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>135874973</v>
       </c>
       <c r="B200" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>135874974</v>
       </c>
       <c r="B201" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135874918</v>
       </c>
       <c r="B203" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135874931</v>
       </c>
       <c r="B204" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>135874933</v>
       </c>
       <c r="B205" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>135881507</v>
       </c>
       <c r="B206" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>135949529</v>
       </c>
       <c r="B207" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>135949675</v>
       </c>
       <c r="B208" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>135949755</v>
       </c>
       <c r="B209" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135950038</v>
       </c>
       <c r="B210" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>135950125</v>
       </c>
       <c r="B211" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>135874947</v>
       </c>
       <c r="B212" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>135874949</v>
       </c>
       <c r="B213" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>135874958</v>
       </c>
       <c r="B214" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>135874966</v>
       </c>
       <c r="B215" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>135874967</v>
       </c>
       <c r="B216" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>135949995</v>
       </c>
       <c r="B217" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135859933</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135858947</v>
       </c>
       <c r="B3" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135859541</v>
       </c>
       <c r="B4" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135859616</v>
       </c>
       <c r="B5" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135859685</v>
       </c>
       <c r="B6" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>135860007</v>
       </c>
       <c r="B7" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135860056</v>
       </c>
       <c r="B8" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135860113</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135864226</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>135864785</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135874927</v>
       </c>
       <c r="B12" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135874917</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>135881476</v>
       </c>
       <c r="B14" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135881481</v>
       </c>
       <c r="B15" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135949111</v>
       </c>
       <c r="B16" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135949581</v>
       </c>
       <c r="B17" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>135881488</v>
       </c>
       <c r="B18" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135881494</v>
       </c>
       <c r="B19" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135881497</v>
       </c>
       <c r="B20" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>135881498</v>
       </c>
       <c r="B21" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135881501</v>
       </c>
       <c r="B22" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135949332</v>
       </c>
       <c r="B23" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>135949339</v>
       </c>
       <c r="B24" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>135949571</v>
       </c>
       <c r="B25" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135949829</v>
       </c>
       <c r="B26" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135949971</v>
       </c>
       <c r="B27" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135950195</v>
       </c>
       <c r="B28" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135950279</v>
       </c>
       <c r="B29" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>135874961</v>
       </c>
       <c r="B30" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135949812</v>
       </c>
       <c r="B31" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135950106</v>
       </c>
       <c r="B32" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>135874946</v>
       </c>
       <c r="B33" t="n">
-        <v>92057</v>
+        <v>92058</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135874952</v>
       </c>
       <c r="B34" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135874970</v>
       </c>
       <c r="B35" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>135874978</v>
       </c>
       <c r="B36" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>135874924</v>
       </c>
       <c r="B37" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>135874945</v>
       </c>
       <c r="B38" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>135874976</v>
       </c>
       <c r="B39" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135881489</v>
       </c>
       <c r="B40" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>135881499</v>
       </c>
       <c r="B41" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135949613</v>
       </c>
       <c r="B42" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>135949619</v>
       </c>
       <c r="B43" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>135949627</v>
       </c>
       <c r="B44" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135949915</v>
       </c>
       <c r="B45" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>135950255</v>
       </c>
       <c r="B46" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135874916</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135874920</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135874922</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135874938</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135874944</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>135874953</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>135874972</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135881474</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>135881483</v>
       </c>
       <c r="B55" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135881485</v>
       </c>
       <c r="B56" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>135881493</v>
       </c>
       <c r="B57" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135881500</v>
       </c>
       <c r="B58" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135881505</v>
       </c>
       <c r="B59" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135949167</v>
       </c>
       <c r="B60" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>135949177</v>
       </c>
       <c r="B61" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135949277</v>
       </c>
       <c r="B62" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135949323</v>
       </c>
       <c r="B63" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>135949328</v>
       </c>
       <c r="B64" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>135949364</v>
       </c>
       <c r="B65" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135949390</v>
       </c>
       <c r="B66" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>135949442</v>
       </c>
       <c r="B67" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135949469</v>
       </c>
       <c r="B68" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135949550</v>
       </c>
       <c r="B69" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135949654</v>
       </c>
       <c r="B70" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>135949666</v>
       </c>
       <c r="B71" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>135949718</v>
       </c>
       <c r="B72" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>135949724</v>
       </c>
       <c r="B73" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>135949734</v>
       </c>
       <c r="B74" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>135949744</v>
       </c>
       <c r="B75" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>135949840</v>
       </c>
       <c r="B76" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>135949862</v>
       </c>
       <c r="B77" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>135949871</v>
       </c>
       <c r="B78" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>135950098</v>
       </c>
       <c r="B79" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>135950119</v>
       </c>
       <c r="B80" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>135950143</v>
       </c>
       <c r="B81" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>135950156</v>
       </c>
       <c r="B82" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>135950224</v>
       </c>
       <c r="B83" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>135950300</v>
       </c>
       <c r="B84" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>135950333</v>
       </c>
       <c r="B85" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>135874943</v>
       </c>
       <c r="B86" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>135859078</v>
       </c>
       <c r="B87" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135874930</v>
       </c>
       <c r="B88" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135874934</v>
       </c>
       <c r="B89" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>135874969</v>
       </c>
       <c r="B90" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135881477</v>
       </c>
       <c r="B91" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>135949521</v>
       </c>
       <c r="B92" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>135949686</v>
       </c>
       <c r="B93" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>135949696</v>
       </c>
       <c r="B94" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>135950288</v>
       </c>
       <c r="B95" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>135874919</v>
       </c>
       <c r="B96" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>135874921</v>
       </c>
       <c r="B97" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>135874923</v>
       </c>
       <c r="B98" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>135874935</v>
       </c>
       <c r="B99" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135874936</v>
       </c>
       <c r="B100" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>135874956</v>
       </c>
       <c r="B101" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>135874957</v>
       </c>
       <c r="B102" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>135881508</v>
       </c>
       <c r="B103" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>135949454</v>
       </c>
       <c r="B104" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>135949462</v>
       </c>
       <c r="B105" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135949558</v>
       </c>
       <c r="B106" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>135950115</v>
       </c>
       <c r="B107" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>135862781</v>
       </c>
       <c r="B108" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>135874959</v>
       </c>
       <c r="B109" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>135874960</v>
       </c>
       <c r="B110" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135874963</v>
       </c>
       <c r="B111" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>135874964</v>
       </c>
       <c r="B112" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>135949350</v>
       </c>
       <c r="B113" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>135874965</v>
       </c>
       <c r="B114" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>135874977</v>
       </c>
       <c r="B115" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>135874962</v>
       </c>
       <c r="B116" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>135855768</v>
       </c>
       <c r="B117" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>135856140</v>
       </c>
       <c r="B118" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>135856416</v>
       </c>
       <c r="B119" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>135860346</v>
       </c>
       <c r="B120" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>135866514</v>
       </c>
       <c r="B121" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>135869093</v>
       </c>
       <c r="B122" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>135874388</v>
       </c>
       <c r="B123" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>135874644</v>
       </c>
       <c r="B124" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>135874687</v>
       </c>
       <c r="B125" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135881482</v>
       </c>
       <c r="B126" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>135881504</v>
       </c>
       <c r="B127" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>135856696</v>
       </c>
       <c r="B128" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>135857596</v>
       </c>
       <c r="B129" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>135863251</v>
       </c>
       <c r="B130" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>135863729</v>
       </c>
       <c r="B131" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>135866611</v>
       </c>
       <c r="B132" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>135866664</v>
       </c>
       <c r="B133" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>135874094</v>
       </c>
       <c r="B134" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>135874206</v>
       </c>
       <c r="B135" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>135874271</v>
       </c>
       <c r="B136" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>135874471</v>
       </c>
       <c r="B137" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135874519</v>
       </c>
       <c r="B138" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135874555</v>
       </c>
       <c r="B139" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>135874571</v>
       </c>
       <c r="B140" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>135874604</v>
       </c>
       <c r="B141" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>135874664</v>
       </c>
       <c r="B142" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>135874939</v>
       </c>
       <c r="B143" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>135874971</v>
       </c>
       <c r="B144" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>135874975</v>
       </c>
       <c r="B145" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135881487</v>
       </c>
       <c r="B146" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>135881506</v>
       </c>
       <c r="B147" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>135855584</v>
       </c>
       <c r="B148" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>135856270</v>
       </c>
       <c r="B149" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>135856477</v>
       </c>
       <c r="B150" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>135856559</v>
       </c>
       <c r="B151" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>135856614</v>
       </c>
       <c r="B152" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135856877</v>
       </c>
       <c r="B153" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>135858582</v>
       </c>
       <c r="B154" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>135858744</v>
       </c>
       <c r="B155" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>135861015</v>
       </c>
       <c r="B156" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135861090</v>
       </c>
       <c r="B157" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>135861887</v>
       </c>
       <c r="B158" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>135862486</v>
       </c>
       <c r="B159" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135862583</v>
       </c>
       <c r="B160" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135862811</v>
       </c>
       <c r="B161" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>135863010</v>
       </c>
       <c r="B162" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>135863047</v>
       </c>
       <c r="B163" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>135863070</v>
       </c>
       <c r="B164" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>135863446</v>
       </c>
       <c r="B165" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>135863630</v>
       </c>
       <c r="B166" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135863743</v>
       </c>
       <c r="B167" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>135863785</v>
       </c>
       <c r="B168" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>135864377</v>
       </c>
       <c r="B169" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>135866322</v>
       </c>
       <c r="B170" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>135867307</v>
       </c>
       <c r="B171" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>135868572</v>
       </c>
       <c r="B172" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>135868617</v>
       </c>
       <c r="B173" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>135868655</v>
       </c>
       <c r="B174" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>135868970</v>
       </c>
       <c r="B175" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>135869055</v>
       </c>
       <c r="B176" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>135869170</v>
       </c>
       <c r="B177" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>135869209</v>
       </c>
       <c r="B178" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>135869293</v>
       </c>
       <c r="B179" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>135869360</v>
       </c>
       <c r="B180" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>135869401</v>
       </c>
       <c r="B181" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>135874124</v>
       </c>
       <c r="B182" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>135874166</v>
       </c>
       <c r="B183" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135874926</v>
       </c>
       <c r="B184" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>135874929</v>
       </c>
       <c r="B185" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>135874941</v>
       </c>
       <c r="B186" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>135874968</v>
       </c>
       <c r="B187" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>135881510</v>
       </c>
       <c r="B188" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135858133</v>
       </c>
       <c r="B192" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>135863529</v>
       </c>
       <c r="B193" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>135874932</v>
       </c>
       <c r="B194" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>135874951</v>
       </c>
       <c r="B195" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>136156620</v>
       </c>
       <c r="B196" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>135874706</v>
       </c>
       <c r="B199" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>135874973</v>
       </c>
       <c r="B200" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>135874974</v>
       </c>
       <c r="B201" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>135949357</v>
       </c>
       <c r="B202" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135874918</v>
       </c>
       <c r="B203" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>135874931</v>
       </c>
       <c r="B204" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>135874933</v>
       </c>
       <c r="B205" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>135881507</v>
       </c>
       <c r="B206" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>135949529</v>
       </c>
       <c r="B207" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>135949675</v>
       </c>
       <c r="B208" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>135949755</v>
       </c>
       <c r="B209" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135950038</v>
       </c>
       <c r="B210" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>135950125</v>
       </c>
       <c r="B211" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>135874947</v>
       </c>
       <c r="B212" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>135874949</v>
       </c>
       <c r="B213" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>135874958</v>
       </c>
       <c r="B214" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>135874966</v>
       </c>
       <c r="B215" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>135874967</v>
       </c>
       <c r="B216" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>135949995</v>
       </c>
       <c r="B217" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
